--- a/ig/DM-JUIN-2026/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T08:50:40+00:00</t>
+    <t>2026-07-02T10:15:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T10:15:38+00:00</t>
+    <t>2026-07-06T14:29:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
